--- a/sample_data/3_Multiple_Transactions_Test.xlsx
+++ b/sample_data/3_Multiple_Transactions_Test.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Juan Dela Cruz Enterprises</t>
+          <t>[TEST] Juan Dela Cruz Enterprises</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>111-222-333-000</t>
+          <t>999-300-100-000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maria Santos Consulting</t>
+          <t>[TEST] Maria Santos Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>444-555-666-000</t>
+          <t>999-300-200-000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
